--- a/Documents/Confessions of HNMU.xlsx
+++ b/Documents/Confessions of HNMU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal\Group Assignments\Lap_trinh_web\ToxicFilter\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD845C1E-D0E4-49E7-9814-B0E449286705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312601C2-5FC0-47D2-ACCA-993F72164E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5084" uniqueCount="3048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5084" uniqueCount="3049">
   <si>
     <t>index</t>
   </si>
@@ -9164,6 +9164,9 @@
   </si>
   <si>
     <t>Hello mọi người</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mê mê mê trường lồn phắc </t>
   </si>
 </sst>
 </file>
@@ -9615,7 +9618,7 @@
         <v>3033</v>
       </c>
       <c r="E6" t="s">
-        <v>3034</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
